--- a/Hoadon/HDVao/1/3502386218_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/1/3502386218_HDDienTuMayTinhTien.xlsx
@@ -211,7 +211,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/01/2026 đến ngày 31/01/2026</t>
+          <t>Từ ngày 01/01/2026 đến ngày 03/01/2026</t>
         </is>
       </c>
     </row>
